--- a/feedback_forms/038_new_design_feedback_form--feedback_forms.xlsx
+++ b/feedback_forms/038_new_design_feedback_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'1',_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': '1', 'label': 'Very good'}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'2',_'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': '2', 'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'3',_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': '3', 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'chatjimmy',_'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'ChatJimmy', 'label': 'ChatJimmy'}</t>
+          <t>ChatJimmy</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'johndoe',_'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'JohnDoe', 'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
